--- a/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
+++ b/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1468,32 +1468,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IF-0008</t>
+          <t>IF-0008 / ENG-SWE3-001 v0.2 5.2절/6.8절(결정표 I, Phase2 갱신)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARC-0005 (Command Arbiter, 게이트 골격)</t>
+          <t>ARC-0005 (Command Arbiter, 게이트 골격 — Phase2 계약 대체)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>candidateCommands 비어있지 않음(Phase1 경계 위반)</t>
+          <t>candidateCommands 비어있지 않음(door=BOTH, priority=1 단일 후보)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NotImplementedError 발생(명시적 거부)</t>
+          <t>더 이상 NotImplementedError로 거부되지 않고 문별 최소-priority 후보 선택으로 정상 처리됨(leftCommand=rightCommand=RELEASE) — Phase1 계약의 완전한 대체 확인</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>오류주입(Fault Injection Test)</t>
+          <t>결정테이블 테스트(Decision Table Testing) — 결정표 I</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>자동(unittest) - tests_integration/test_it_step4_*.py::TestIT0020CandidateCommandsOutOfPhase1ScopeRaises.testNonEmptyCandidateCommandsRaisesNotImplementedError</t>
+          <t>자동(unittest) - tests_integration/test_it_step4_command_arbiter.py::TestIT0020CandidateCommandsAreArbitratedByPriority.testNonEmptyCandidateCommandsAreResolvedByMinimumPriority</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2345,1856 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>자동(unittest) - tests_integration/test_it_step7_*.py::TestIT0043FullRegressionAcrossStates.testNormalDegradedFaultSequenceRegressesCleanlyThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>IT-0044</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IF-0016 / SWR-007, 결정표 E</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ARC-0010 (충돌 감시)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>status=CONFIRMED, releaseCandidate(door=BOTH, command=RELEASE, priority=1, reasonCode=CRASH_CONFIRMED)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step8_crash_monitor.py::TestIT0044CrashConfirmedProducesReleaseCandidate.testConfirmedYieldsBothDoorReleaseCandidatePriorityOne</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>IT-0045</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IF-0016 / SWR-008, 결정표 E</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ARC-0010 (충돌 감시)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>crash_status=PENDING</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>releaseCandidate=None, pendingHoldApplied=True(긴급해제 미개시)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step8_crash_monitor.py::TestIT0045CrashPendingAppliesHoldWithoutCandidate.testPendingYieldsNoCandidateAndHoldApplied</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>IT-0046</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IF-0016 / 결정표 E</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ARC-0010 (충돌 감시)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>crash_status=NONE(유효값)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>status=NONE, releaseCandidate=None, pendingHoldApplied=False</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step8_crash_monitor.py::TestIT0046CrashNoneYieldsNoCandidate.testValidNoneStatusYieldsNoCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>IT-0047</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IF-0016 / 9장 확인 필요 항목 재확인</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ARC-0010 (충돌 감시)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>crashStatusField.valid=False(정의된 3개 열거값 외)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>예외 없이 status=NONE으로 방어적 처리(새 능동 후보 미생성)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step8_crash_monitor.py::TestIT0047InvalidCrashStatusFieldYieldsNoneWithoutException.testInvalidFieldIsTreatedAsNoneWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>IT-0048</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IF-0016 / 방어적 계약</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ARC-0010 (충돌 감시)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>crashStatusField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step8_crash_monitor.py::TestIT0048CrashStatusFieldNoneContractViolationRaises.testCrashStatusFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IT-0049</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IF-0017 / SWR-005, SWR-009, 결정표 F(FF)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>left=False, right=False</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>leftRiskActive=rightRiskActive=False, 후보/이유코드 없음</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0049BothFalseYieldsNoCandidateOnEitherDoor.testFalseFalseCombinationYieldsNoRiskOnEitherSide</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IT-0050</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IF-0017 / SWR-005, SWR-009, 결정표 F(FT)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>left=True, right=False</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LEFT만 LOCK 억제 후보(priority=2, APPROACH_RISK_LEFT), RIGHT 미영향</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0050LeftTrueRightFalseYieldsOnlyLeftCandidate.testLeftTrueRightFalseCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IT-0051</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IF-0017 / SWR-005, SWR-009, 결정표 F(TF)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>left=False, right=True</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RIGHT만 LOCK 억제 후보(APPROACH_RISK_RIGHT), LEFT 미영향</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0051RightTrueLeftFalseYieldsOnlyRightCandidate.testRightTrueLeftFalseCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IT-0052</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IF-0017 / SWR-005, SWR-009, 결정표 F(TT)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>left=True, right=True</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>좌/우 각각 독립적으로 LOCK 억제 후보 생성</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0052BothTrueYieldsIndependentCandidatesOnBothDoors.testTrueTrueCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>IT-0053</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IF-0017 / 9장 확인 필요 항목 재확인</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>leftApproachRiskField.valid=False</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>예외 없이 leftRiskActive=False로 방어적 처리</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0053InvalidFieldTreatedAsNoRisk.testInvalidLeftFieldYieldsNoRiskWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IT-0054</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IF-0017 / 방어적 계약</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ARC-0011 (접근위험 평가)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>leftApproachRiskField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step9_approach_risk_evaluator.py::TestIT0054FieldNoneContractViolationRaises.testEitherFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IT-0055</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IF-0018 / SWR-006, 결정표 G</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>riskActive=True, releaseReRequested=False</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=False(억제 유지)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0055RiskActiveWithoutReRequestYieldsNoOverride.testRiskActiveButNoReleaseReRequestedYieldsSuppressionMaintained</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>IT-0056</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IF-0018 / SWR-006(a), 경계값분석</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>최초 억제 후 정확히 10.0초 경과 시점 재입력(경계값)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=True, reasonCode=APPROACH_RISK_OVERRIDE_LEFT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0056OverrideActiveAtExactlyTenSecondBoundary.testExactlyTenSecondsElapsedYieldsOverrideActive</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IT-0057</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>IF-0018 / SWR-006(b), 경계값분석</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>최초 억제 후 10.1초 경과 시점 재입력(경계값 바로 위)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=False(억제 유지)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0057OverrideNotActiveJustOverTenSecondBoundary.testTenPointOneSecondsElapsedYieldsOverrideNotActive</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>IT-0058</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IF-0018 / 결정표 G(riskActive=False)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>riskActive=False, releaseReRequested=True</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>override 불성립, 타이머 즉시 리셋</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0058RiskInactiveResetsTimerRegardlessOfReRequest.testRiskInactiveYieldsNoOverrideAndClearsTimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>IT-0059</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IF-0018 / SWR-009 승계</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>좌측 override 성립 조건, 우측은 무관 상태</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=True, rightOverrideActive=False(좌우 완전 독립)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0059LeftAndRightDoorsAreFullyIndependent.testLeftOverrideDoesNotAffectRightDoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>IT-0060</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IF-0018 / 8.6절 상태전이(타이머 리셋 규칙)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>억제-&gt;해제-&gt;재억제(re-entry) 후 9초 경과 재입력</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>새 10초 윈도우가 시작되어 override 성립(이전 억제 시각 오염 없음)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0060SuppressionRestartsAfterRiskClearsAndReturns.testRiskClearsThenReactivatesStartsNewTenSecondWindow</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IT-0061</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>IF-0018 / 8.6절 상태전이(reset())</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ARC-0012 (접근위험 override 판정기)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>억제 유지 중 reset() 호출 후 즉시 재입력</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>reset()이 최초 억제 시각을 지워 override 성립(부팅 기본값 복귀)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step10_override_manager.py::TestIT0061ResetClearsSuppressionTimer.testResetClearsTimerEvenWhileRiskStaysActive</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IT-0062</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>IF-0019 / SWR-017, 결정표 H(단독)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>fire_detected=True(단독)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[FIRE_DETECTED], releaseCandidate(priority=3, BOTH, RELEASE)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0062FireOnlyTriggersForcedRelease.testFireDetectedAloneTriggersRelease</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IT-0063</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>IF-0019 / SWR-017, 결정표 H(단독)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>overtemperature_detected=True(단독)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[OVERTEMPERATURE_DETECTED]</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0063OvertemperatureOnlyTriggersForcedRelease.testOvertemperatureAloneTriggersRelease</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IT-0064</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IF-0019 / SWR-017, 결정표 H(단독)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>adult_present=True(단독)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[ADULT_PRESENT_DETECTED]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0064AdultPresentOnlyTriggersForcedRelease.testAdultPresentAloneTriggersRelease</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IT-0065</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IF-0019 / SWR-017, 결정표 H(복합)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>fire/overtemp/adult 3개 모두 True</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>reasonCodes=[FIRE_DETECTED,OVERTEMPERATURE_DETECTED,ADULT_PRESENT_DETECTED] 전부 기록</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0065AllThreeSimultaneouslyRecordsAllReasonCodes.testAllThreeTrueRecordsAllThreeReasonCodesInOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IT-0066</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IF-0019 / 결정표 H(전부 FALSE)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>fire/overtemp/adult 3개 모두 False</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>triggered=False, releaseCandidate=None, triggeredReasonCodes=[]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0066AllFalseYieldsNoTrigger.testAllFalseYieldsNoTriggerAndNoCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IT-0067</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>IF-0019 / 9장 확인 필요 항목 재확인</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>fireField.valid=False</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>예외 없이 FALSE(트리거 미기여)로 방어적 처리</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0067InvalidFieldTreatedAsFalse.testInvalidFireFieldIsTreatedAsFalseWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IT-0068</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IF-0019 / 방어적 계약</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ARC-0013 (화재/과온/탑승 감시)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>overtempField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step11_fire_overtemp_occupant_monitor.py::TestIT0068AnyFieldNoneContractViolationRaises.testAnyFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IT-0069</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0016/IF-0017 / SWR-005,007, 결정표 I, 7장 시나리오7</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>crash(priority=1,BOTH,RELEASE) + 접근위험(priority=2,LEFT,LOCK) 동시 존재</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>leftCommand=rightCommand=RELEASE(priority=1 승리, 접근위험 억제 철회)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0069CrashPriorityWinsOverApproachRiskOnBothDoors.testCrashCandidateOverridesLeftApproachRiskSuppression</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>IT-0070</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0017/IF-0019 / SWR-005,017, 결정표 I</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>접근위험(priority=2,LEFT,LOCK) + 화재(priority=3,BOTH,RELEASE) 동시 존재</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>leftCommand=LOCK(priority=2 승리), rightCommand=RELEASE(priority=3만 적용)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0070ApproachRiskPriorityWinsOverFireOnLeftDoor.testApproachRiskCandidateOverridesFireOnLeftButNotRight</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IT-0071</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0017 / SWR-009, 결정표 I(문별 독립성)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LEFT 전용 후보만 존재(RIGHT 후보 없음)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>leftCommand=LOCK, rightCommand=NO_CHANGE(적용 가능 후보 없음)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0071DoorSpecificCandidateDoesNotAffectOtherDoor.testLeftOnlyCandidateLeavesRightAsNoChange</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>IT-0072</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IF-0008 / 결정표 I 비고(불변조건)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>동일 문(BOTH)에 동일 최소 priority(1) 후보 2개</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ValueError 발생(설계상 발생 불가한 불변조건 위반)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0072DuplicateMinimumPriorityOnSameDoorRaises.testTwoCandidatesWithSamePriorityOnSameDoorRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>IT-0073</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IF-0008 / 8장 Phase2 확정 사항, 회귀(1~4단계)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>state=FAULT + 충돌/접근위험/화재 후보 모두 존재</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>blocked=True/STATE_FAULT(Phase2 후보 전부 차단, Phase1 게이트 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0073FaultGateBlocksAllPhase2Candidates.testFaultStateBlocksEvenWithNonEmptyPhase2Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IT-0074</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IF-0008 / 결정표 D 유지, 회귀(1~4단계)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 규칙 체인 확장)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>inputValid=False + 화재 후보 존재</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>blocked=True/INPUT_INVALID(Phase2 후보 차단, Phase1 게이트 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step12_command_arbiter_priority_chain.py::TestIT0074InputInvalidGateBlocksAllPhase2Candidates.testInputInvalidBlocksEvenWithNonEmptyPhase2Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IT-0075</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IF-0013 / SWR-007, 결정표 E 입력 경로</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>rawCrashStatus="CONFIRMED"</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>valid=True, value=CrashStatus.CONFIRMED</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0075ValidCrashStatusEnumStringIsAccepted.testConfirmedStringIsParsedToCrashStatusEnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IT-0076</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IF-0013 / OEM-IF-002 공통 규칙</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>rawCrashStatus="BOGUS_STATUS"(미정의 열거값)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=INVALID_ENUM_VALUE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0076InvalidCrashStatusEnumValueIsRejected.testUnknownEnumStringIsRejectedWithInvalidEnumReason</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IT-0077</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IF-0013 / OEM-IF-002 공통 규칙</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>rawCrashStatus=None(누락)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=MISSING</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0077MissingCrashStatusIsRejected.testNoneRawValueIsRejectedAsMissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>IT-0078</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IF-0013 / OEM-IF-002 공통 규칙</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>rawCrashStatus=1(정수, 형식 오류)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0078NonStringCrashStatusIsRejectedAsTypeError.testIntegerRawValueIsRejectedAsTypeError</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IT-0079</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IF-0014 / SWR-005, SWR-009</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>rear_left_approach_risk=True, rear_right_approach_risk=False</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>좌/우 각각 독립적으로 valid=True, value 보존(값 혼선 없음)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0079ApproachRiskBooleanFieldsValidatedIndependently.testLeftTrueRightFalseAreValidatedIndependently</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IT-0080</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IF-0015 / SWR-017, OEM-IF-007 공통 규칙</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>fire_detected="yes"(문자열, 형식 오류)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0080FireSeriesNonBooleanIsRejectedAsTypeError.testNonBooleanFireDetectedIsRejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IT-0081</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IF-0005(확장) / SWR-013 회귀 확인</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Phase1 3필드 + Phase2 6필드 동시 포함 원시 입력 1건</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NormalizedSafetyInput 9필드 모두 정상 조립, Phase1 필드 정규화 결과 불변(회귀 없음)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0081NormalizeCycleAssemblesAllNineFieldsWithoutRegression.testNormalizeCycleAssemblesPhase2FieldsWithoutBreakingPhase1Fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IT-0082</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0013,IF-0016 / SWR-007 인수기준, 7장 시나리오4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>crash_status=CONFIRMED 원시 입력(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>좌/우 RELEASE로 확정(300ms 예산 내, tick=50ms)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0082CrashConfirmedFullChainReleasesBothDoors.testCrashConfirmedRawInputYieldsBothDoorReleaseThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IT-0083</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0014,IF-0017 / SWR-005,009 인수기준, 7장 시나리오5</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>rear_left/right_approach_risk=True(둘 다) 원시 입력(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>좌/우 모두 LOCK 억제로 독립 확정</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0083ApproachRiskFullChainLocksBothDoorsIndependently.testLeftAndRightApproachRiskYieldsIndependentLockThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IT-0084</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>IF-0018 / SWR-006, ledger 갭7(적용 한계)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>좌측 억제 후 15초 경과 재평가(원시 입력, releaseReRequested 채널 미연결)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>override 불성립, LEFT LOCK 억제 계속 유지(placeholder 한계 문서화)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0084OverrideNeverActivatesThroughFullChainDueToPlaceholder.testSuppressionPersistsBeyondTenSecondsBecauseReleaseReRequestedPlaceholderIsAlwaysFalse</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IT-0085</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0015,IF-0019 / SWR-017 인수기준, 7장 시나리오6</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>fire_detected=True 원시 입력(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>좌/우 RELEASE로 확정</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0085FireFullChainReleasesBothDoors.testFireDetectedRawInputYieldsBothDoorReleaseThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IT-0086</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IF-0016~IF-0019,IF-0008 / SWR-005,007,017 우선순위 중재, 7장 시나리오7</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>crash CONFIRMED + left approach risk True + fire True 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>충돌(priority=1)이 우선해 좌/우 모두 RELEASE</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>유스케이스 테스트(Use Case Testing)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0086MultiConditionPriorityMediationFullChain.testCrashApproachRiskAndFireSimultaneouslyYieldsCrashPriorityOnBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IT-0087</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>IF-0006~IF-0019 / 11장 통합 순서, 3장/7장 고정 호출 순서</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>실물 컴포넌트 1주기 평가, 호출 순서 계측(Phase2 4개 리프 포함)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>IF-0006-&gt;0007-&gt;0016-&gt;0017-&gt;0018-&gt;0019-&gt;0008-&gt;0009-&gt;0010-&gt;0011-&gt;0012 순서로 각 1회</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>유스케이스 테스트(Use Case Testing)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0087FixedCallOrderAcrossPhase2RealComponents.testAllElevenSubComponentsCalledInArchitectureOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IT-0088</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IF-0007~IF-0009,IF-0016 / 8장 Phase2 확정, 오류주입, 회귀</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>sensor_fault=True + crash_status=CONFIRMED 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>state=FAULT, fail-freeze 유지(FAULT가 Phase2 후보보다 항상 우선)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0088FaultGateOverridesSimultaneousCrashCandidateFullChain.testSensorFaultTrueForcesFailFreezeEvenWithCrashConfirmedSimultaneously</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>IT-0089</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IF-0006,IF-0007,IF-0016 / 8장 Phase2 확정(갭4), 회귀</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>freshness 200ms 초과(DEGRADED) + crash_status=CONFIRMED 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>state=DEGRADED이지만 crash RELEASE 후보는 제한 없이 적용</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0089DegradedDoesNotBlockPhase2CandidatesFullChain.testStaleFreshnessDoesNotPreventCrashConfirmedReleaseFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>IT-0090</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>IF-0001,IF-0002,IF-0005,IF-0007,IF-0009 / SWR-021 인수기준 재실행, 회귀</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Phase2 원시 필드 미제공(하위호환) + sensor_fault=True 첫 주기</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>fail-freeze + FAULT 경고 발행 그대로 유지(Phase1 인수기준 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0090Phase1AcceptanceStillPassesThroughExtendedOrchestrator.testSensorFaultTrueFullChainAcceptanceUnaffectedByPhase2Extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>IT-0091</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>IF-0018 내부 reset 경로 / 8.6절, 13장 자원 경계</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>orchestrator.reset() 호출(overrideManager 계측)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>overrideManager.reset()이 정확히 1회 호출됨(계단식 reset 확장 확인)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0091ResetCascadesToOverrideManagerAtOrchestratorLevel.testOrchestratorResetCallsOverrideManagerReset</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>IT-0092</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IF-0005(확장)/IF-0008 결정표 D 근거, 오류주입</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0010~0013 호출 및 candidateCommands 조립 추가)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>fire_detected 형식 오류(무효) + crash_status=CONFIRMED 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>무관한 fire 필드 무효가 crash RELEASE 후보를 차단하지 않음(결정표 D 근거 실증)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step14_orchestrator_phase2_integration.py::TestIT0092InvalidFireFieldDoesNotBlockUnrelatedCrashCandidateFullChain.testInvalidFireFieldDoesNotSuppressCrashConfirmedReleaseFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IT-0093</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IF-0013 / 5.1절 비고(이미 파싱된 인스턴스 경로)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, 신규 필드 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>rawCrashStatus=CrashStatus.PENDING(이미 파싱된 enum 인스턴스)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>재파싱 없이 valid=True, value=CrashStatus.PENDING 그대로 수용</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0093CrashStatusEnumInstanceIsAcceptedDirectly.testAlreadyCrashStatusInstanceIsAcceptedWithoutReparsing</t>
         </is>
       </c>
     </row>
@@ -2375,7 +4225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2541,6 +4391,38 @@
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2(안전 긴급 대응) 확장 — ENG-SWE2-001 v0.2 11장 8~14단계를 따라 IT-0044~IT-0093(50건, IT-0093은 5.1절 비고 경로 보완) 신규 작성. IF-0016~IF-0019(신규 리프 4종) 및 확장된IF-0005/IF-0008/IF-0013~IF-0015 전체를 대상으로 오류 주입(ASIL B 경로) 포함. 기존 IT-0020은IU-0005 계약 대체(Phase1 NotImplementedError → 문별 우선순위 선택)에 맞춰 갱신. 작성 중 오기(행 오프셋 오류로 IT-0021 행이 일시 덮어써짐)를 같은 세션에서 발견·정정함(원본 내용 복원 확인).</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
+++ b/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-002_SW 통합시험 케이스.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.3 (Draft) — Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -4195,6 +4195,1745 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>자동(unittest) - tests_integration/test_it_step13_input_validation_adapter_extended.py::TestIT0093CrashStatusEnumInstanceIsAcceptedDirectly.testAlreadyCrashStatusInstanceIsAcceptedWithoutReparsing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IT-0094</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>IF-0023 / SWR-020(a), 결정표 N</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ARC-0016 (ignition-off 해제 후보 생성)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ignitionOnField valid=True/value=False</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>off=True, releaseCandidate(BOTH,RELEASE,priority=4,IGNITION_OFF)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step15_ignition_off_release_monitor.py::TestIT0094ValidFalseYieldsReleaseCandidatePriorityFour.testValidIgnitionOffYieldsBothDoorReleaseCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IT-0095</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IF-0023 / SWR-020, 결정표 N</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ARC-0016 (ignition-off 해제 후보 생성)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ignitionOnField valid=True/value=True</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>off=False, releaseCandidate 없음</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step15_ignition_off_release_monitor.py::TestIT0095ValidTrueYieldsNoCandidate.testValidIgnitionOnYieldsNoCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IT-0096</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IF-0023 / ENG-SWE3-001 8.8절, 오류주입</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ARC-0016 (ignition-off 해제 후보 생성)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ignitionOnField.valid=False(형식 오류)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>예외 없이 off=False, 후보 미생성</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step15_ignition_off_release_monitor.py::TestIT0096InvalidFieldYieldsNoCandidateWithoutException.testInvalidFieldIsTreatedAsNotOffWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IT-0097</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IF-0023 / 방어적 계약, 오류주입</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ARC-0016 (ignition-off 해제 후보 생성)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ignitionOnField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step15_ignition_off_release_monitor.py::TestIT0097IgnitionOnFieldNoneContractViolationRaises.testIgnitionOnFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IT-0098</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IF-0022 / SWR-018(a)/(b), 결정표 M(FF)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>isofixLeft=False, isofixRight=False</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>양쪽 모두 lockActive=False, 후보 없음</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0098BothFalseYieldsNoCandidateOnEitherDoor.testFalseFalseCombinationYieldsNoLockOnEitherSide</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IT-0099</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IF-0022 / SWR-018(a)/(b), 결정표 M(FT)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>isofixLeft=True, isofixRight=False</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LEFT만 lockCandidate(LEFT,LOCK,priority=5), RIGHT 무영향</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0099LeftTrueRightFalseYieldsOnlyLeftCandidate.testLeftTrueRightFalseCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IT-0100</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IF-0022 / SWR-018(a)/(b), 결정표 M(TF)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>isofixLeft=False, isofixRight=True</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RIGHT만 lockCandidate, LEFT 무영향</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0100RightTrueLeftFalseYieldsOnlyRightCandidate.testRightTrueLeftFalseCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IT-0101</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IF-0022 / SWR-018(a)/(b), 결정표 M(TT)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>isofixLeft=True, isofixRight=True</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>양쪽 모두 독립적으로 lockCandidate 생성</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0101BothTrueYieldsIndependentCandidatesOnBothDoors.testTrueTrueCombination</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IT-0102</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>IF-0022 / 9장 확인 필요 항목, 오류주입</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>isofixLeftField.valid=False</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>예외 없이 leftLockActive=False, 후보 미생성</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0102InvalidLeftFieldTreatedAsNoLockWithoutException.testInvalidLeftFieldYieldsNoLockWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IT-0103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>IF-0022 / 방어적 계약, 오류주입</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ARC-0015 (ISOFIX 강제잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>isofixLeftField 또는 isofixRightField=None</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step16_isofix_forced_lock_monitor.py::TestIT0103IsofixFieldNoneContractViolationRaises.testEitherFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IT-0104</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IF-0021 / SWR-003(a), 결정표 L, 경계값분석</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ARC-0014 (차속 자동주행잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph=2.9(임계 미만)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>locked=False, lockCandidate 없음</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py::TestIT0104BelowThresholdYieldsNoCandidate.testSpeed29YieldsNotLocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IT-0105</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IF-0021 / SWR-003(a), 결정표 L, 경계값분석</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ARC-0014 (차속 자동주행잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph=3.0(임계값 자체)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>locked=True, lockCandidate(BOTH,LOCK,priority=6,AUTO_DRIVE_LOCK)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py::TestIT0105AtThresholdYieldsLockCandidatePrioritySix.testSpeedExactly30YieldsLockedWithCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>IT-0106</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IF-0021 / SWR-003(a), 결정표 L, 경계값분석</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ARC-0014 (차속 자동주행잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph=3.1(임계 초과)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>locked=True, lockCandidate 생성</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py::TestIT0106AboveThresholdYieldsLockCandidate.testSpeed31YieldsLocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IT-0107</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IF-0021 / 9장 확인 필요 항목, 오류주입</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ARC-0014 (차속 자동주행잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>vehicleSpeedField.valid=False(범위 밖)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>예외 없이 locked=False, 후보 미생성</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py::TestIT0107InvalidFieldYieldsNoCandidateWithoutException.testInvalidFieldIsTreatedAsNotLockedWithoutRaising</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IT-0108</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IF-0021 / 방어적 계약, 오류주입</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARC-0014 (차속 자동주행잠금 감시)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>vehicleSpeedField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py::TestIT0108VehicleSpeedFieldNoneContractViolationRaises.testVehicleSpeedFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IT-0109</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0022/IF-0023 / SWR-018,020, 9장, 7장 시나리오 11</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ignition-off(priority=4,BOTH,RELEASE) + ISOFIX(priority=5,LEFT,LOCK) 동시</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LEFT/RIGHT 모두 RELEASE</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0109IgnitionOffPriorityWinsOverIsofixOnLeftDoor.testIgnitionOffReleaseOverridesIsofixLockOnLeftDoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IT-0110</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0021/IF-0023 / SWR-003,020, 9장</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ignition-off(priority=4,RELEASE) + 자동주행잠금(priority=6,LOCK) 동시</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>양쪽 모두 RELEASE</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0110IgnitionOffPriorityWinsOverAutoDriveLock.testIgnitionOffReleaseOverridesAutoDriveLockOnBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IT-0111</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0021/IF-0022 / SWR-003,018, 9장</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ISOFIX(priority=5,LEFT,LOCK) + 자동주행잠금(priority=6,BOTH,LOCK) 동시</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LEFT는 ISOFIX 이유코드로 LOCK, RIGHT는 자동주행잠금 이유코드로 LOCK</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0111IsofixPriorityWinsOverAutoDriveLockOnSameDoor.testIsofixReasonCodeIsSelectedOverAutoDriveLockOnLeftDoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IT-0112</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0017/IF-0023 / 누적 갭 16(현재 동작 문서화)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>접근위험(priority=2,LEFT,LOCK) + ignition-off(priority=4,BOTH,RELEASE) 동시</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LEFT=LOCK(접근위험 승리, 갭16 미해소 현재 동작), RIGHT=RELEASE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0112ApproachRiskPriorityWinsOverIgnitionOffCurrentBehavior.testApproachRiskSuppressionCurrentlyOverridesIgnitionOffOnLeftDoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IT-0113</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IF-0008/IF-0019/IF-0022 / SWR-017,018, 9장</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>화재 등(priority=3,BOTH,RELEASE) + ISOFIX(priority=5,BOTH,LOCK) 동시</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>양쪽 모두 RELEASE</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0113FirePriorityWinsOverIsofixForcedLock.testFireForcedReleaseOverridesIsofixLockOnBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IT-0114</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IF-0008 / 8장 Phase3 확정 사항, 회귀(1~4,8~12단계)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>state=FAULT + Phase3 후보 3종 모두 존재</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>blocked=True/STATE_FAULT, 좌우 NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0114FaultGateBlocksAllPhase3Candidates.testFaultStateBlocksEvenWithNonEmptyPhase3Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IT-0115</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IF-0008 / 결정표 D 유지, 회귀(1~4,8~12단계)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>inputValid=False + Phase3 후보 존재</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>blocked=True/INPUT_INVALID</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0115InputInvalidGateBlocksAllPhase3Candidates.testInputInvalidBlocksEvenWithNonEmptyPhase3Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IT-0116</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IF-0008 / 결정표 I 비고(불변조건), 오류주입</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ARC-0005 (Command Arbiter, 우선순위 체인 확장 — 4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>동일 문에 동일 최소 priority(=5) 후보 2개</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py::TestIT0116DuplicateMinimumPriorityAmongPhase3CandidatesRaises.testTwoPhase3CandidatesWithSamePriorityOnSameDoorRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>IT-0117</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IF-0007 / SWR-013(a), 회귀(2단계), 결정표 K</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ignitionOnField valid=True/True, stale=False, fault=False</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>state=NORMAL(회귀 기준선)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0117IgnitionOnDoesNotForceOffRegression.testIgnitionOnValidTrueWithNoOtherConditionYieldsNormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IT-0118</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IF-0007 / SWR-020(a)/(b), 결정표 K, 7장 시나리오 10</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ignitionOnField valid=True/False, fault=False</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>state=OFF, warningReasonCode=IGNITION_OFF</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0118IgnitionOffYieldsOffStateWithWarningCode.testIgnitionOnValidFalseYieldsOffState</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IT-0119</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IF-0007 / 8장 FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL, 결정표 K</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>fault=True + ignition-off 동시</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>state=FAULT(FAULT가 OFF보다 우선)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0119FaultPriorityOverOff.testSensorFaultTrueAndIgnitionOffSimultaneouslyYieldsFaultNotOff</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>IT-0120</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IF-0007 / 8장 FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL, 결정표 K</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ignition-off + stale=True 동시</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>state=OFF(OFF가 DEGRADED보다 우선)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0120OffPriorityOverDegraded.testIgnitionOffAndStaleSimultaneouslyYieldsOffNotDegraded</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>IT-0121</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IF-0007 / ENG-SWE3-001 8.8절, 오류주입</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ignitionOnField.valid=False(형식 오류)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>state=NORMAL(OFF로 판정되지 않음, freshness/NORMAL 경로 대체)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0121InvalidIgnitionFieldDoesNotForceOffAndFallsBackToNormalPath.testIgnitionOnFieldInvalidIsNotJudgedAsOff</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IT-0122</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IF-0007 / 방어적 계약, ASIL B 오류 주입</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ignitionOnField=None(상위 계약 위반)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ValueError 발생</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0122IgnitionOnFieldNoneContractViolationRaises.testIgnitionOnFieldNoneRaisesValueError</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IT-0123</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>IF-0007 / 결정표 K 전체, 전 조건 조합</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ARC-0003 (상태 관리자, OFF 상태 추가 — FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>fault/ignitionOff/stale 3조건 8개 조합 전수</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>각 조합이 결정표 K(FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL)와 정확히 일치</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>결정테이블 테스트(Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step19_state_manager_off_state.py::TestIT0123FourStateExhaustiveCombinationTable.testAllEightFaultIgnitionStaleCombinationsMatchDecisionTableK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IT-0124</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>IF-0001(vehicle_speed_kph) / SWR-003, 요구사항 기반 시험</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>rawVehicleSpeedKph=50.0(범위 내)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>valid=True, value=50.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0124ValidVehicleSpeedWithinRangeIsAccepted.testSpeedWithinRangeIsParsedAsFloat</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IT-0125</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IF-0001(vehicle_speed_kph) / SWR-003, 경계값분석</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>rawVehicleSpeedKph=-1.0(하한 미만)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=OUT_OF_RANGE</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0125VehicleSpeedBelowMinimumIsRejected.testNegativeSpeedIsRejectedAsOutOfRange</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IT-0126</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IF-0001(vehicle_speed_kph) / SWR-003, 경계값분석</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>rawVehicleSpeedKph=300.1(상한 초과)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=OUT_OF_RANGE</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0126VehicleSpeedAboveMaximumIsRejected.testSpeedAbove300IsRejectedAsOutOfRange</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IT-0127</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IF-0001(vehicle_speed_kph) / OEM-IF-001 공통 규칙, 동등분할</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>rawVehicleSpeedKph="fast"(숫자 변환 불가)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0127VehicleSpeedNonNumericIsRejectedAsTypeError.testNonNumericSpeedIsRejectedAsTypeError</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IT-0128</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IF-0001(vehicle_speed_kph) / OEM-IF-001 공통 규칙, 동등분할</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>rawVehicleSpeedKph=None(누락)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=MISSING</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0128VehicleSpeedMissingIsRejectedAsMissing.testNoneRawValueIsRejectedAsMissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IT-0129</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>IF-0020(isofix_left/right) / SWR-018, 요구사항 기반 시험</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>isofix_left=True, isofix_right=False(독립 검증)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>각각 valid=True, value 보존, 좌우 독립</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0129IsofixBooleanFieldsValidatedIndependently.testLeftTrueRightFalseAreValidatedIndependently</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IT-0130</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>IF-0005(확장) / SWR-013/005~017 회귀 확인, 요구사항 기반 시험</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ARC-0001 (입력 검증 어댑터, IF-0001 잔여필드[vehicle_speed_kph]·IF-0020[isofix_left/right] 검증 확장)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>12필드(Phase1 3 + Phase2 6 + Phase3 3) 전체 원시 입력</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>normalizeCycle()이 12필드 모두 올바르게 정규화, 기존 필드 훼손 없음</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py::TestIT0130NormalizeCycleAssemblesAllTwelveFieldsWithoutRegression.testNormalizeCycleAssemblesPhase3FieldsWithoutBreakingPriorFields</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IT-0131</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0021 / SWR-003 인수기준, 7장 시나리오 8</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>직전 RELEASE 확정 상태에서 ignition ON + vehicle_speed_kph=3.0(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>좌/우 모두 LOCK으로 전환(후보에 의한 실제 전환 증명)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0131AutoDriveLockFullChainLocksBothDoors.testVehicleSpeedAtThresholdFlipsPreviousReleaseBackToLockThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>IT-0132</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0020,IF-0022 / SWR-018 인수기준, 7장 시나리오 9</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>직전 RELEASE 확정 상태에서 ignition ON + isofix_left=True(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LEFT만 LOCK, RIGHT는 RELEASE 유지(좌우 독립 실증)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0132IsofixFullChainLocksLeftIndependentlyOfRight.testLeftIsofixFlipsOnlyLeftDoorBackToLockThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>IT-0133</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0011,IF-0023 / SWR-020 인수기준, 7장 시나리오 10</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ignition_on=False 원시 입력(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>좌/우 RELEASE 확정 + state=OFF + warningReasonCode=IGNITION_OFF</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0133IgnitionOffFullChainReleasesBothDoorsAndEntersOffState.testIgnitionOffRawInputYieldsBothDoorReleaseAndOffStateThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>IT-0134</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>IF-0021~IF-0023,IF-0008 / 9장 우선순위 체인 확정, 7장 시나리오 11</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>isofix_left=True + ignition_on=False 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>좌/우 모두 RELEASE(ignition-off 승리)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>유스케이스 테스트(Use Case Testing)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0134IsofixVsIgnitionOffPriorityMediationFullChain.testIgnitionOffReleaseWinsOverIsofixLockOnLeftDoorThroughFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>IT-0135</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IF-0017,IF-0023,IF-0008 / 누적 갭 16(현재 동작 문서화)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>rear_left_approach_risk=True + ignition_on=False 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LEFT=LOCK(접근위험 승리, 갭16 미해소 현재 동작), RIGHT=RELEASE</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>유스케이스 테스트(Use Case Testing)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0135ApproachRiskVsIgnitionOffCurrentBehaviorFullChain.testApproachRiskSuppressionCurrentlyWinsOverIgnitionOffOnLeftDoorFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>IT-0136</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IF-0006~IF-0023 / 11장 통합 순서, 3.1절 고정 호출 순서(Phase3 확장)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>정상 입력 1주기, 14개 협력객체 전부 계측</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>IF-0006→0007→0016→0017→0018→0019→0023→0022→0021→0008→0009→0010→0011→0012 순서로 각 1회 호출</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>유스케이스 테스트(Use Case Testing)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0136FixedCallOrderAcrossPhase3RealComponents.testAllFourteenSubComponentsCalledInArchitectureOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>IT-0137</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>IF-0005(확장)/IF-0008 결정표 D 근거, 오류주입</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph 형식 오류 + crash_status=CONFIRMED 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>무관한 vehicleSpeedField 무효가 crash RELEASE 후보를 차단하지 않음</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0137InvalidVehicleSpeedFieldDoesNotBlockUnrelatedCrashCandidateFullChain.testInvalidVehicleSpeedFieldDoesNotSuppressCrashConfirmedReleaseFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IT-0138</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>IF-0005(확장)/IF-0008 결정표 D 근거, 오류주입</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>isofix_left 형식 오류 + crash_status=CONFIRMED 동시(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>무관한 isofixLeftField 무효가 crash RELEASE 후보를 차단하지 않음</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0138InvalidIsofixFieldDoesNotBlockUnrelatedCrashCandidateFullChain.testInvalidIsofixFieldDoesNotSuppressCrashConfirmedReleaseFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>IT-0139</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>IF-0005,IF-0007,IF-0008 / ENG-SWE3-001 8.8절, 오류주입, 회귀</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ignition_on 형식 오류(불리언 아님, 전체 체인)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>state=NORMAL(OFF 미판정) + INPUT_INVALID 차단(확정 출력은 부팅 기본값 유지)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>오류주입(Fault Injection Test)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0139InvalidIgnitionOnFieldDoesNotForceOffFullChain.testInvalidIgnitionOnFieldBlocksCycleAndDoesNotJudgeOffFullChain</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>IT-0140</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IF-0001,IF-0002,IF-0005,IF-0007,IF-0009 / SWR-021/007 인수기준 재실행, 회귀</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ARC-0009 (오케스트레이터, ARC-0014~0016 호출·candidateCommands 조립 확장, ignitionOnField를 ARC-0003에 전달)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Phase3 원시 필드 미제공(하위호환) + sensor_fault=True 두번째 주기</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>fail-freeze + FAULT 경고 발행 그대로 유지(Phase1/2 인수기준 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_integration/test_it_step21_orchestrator_phase3_integration.py::TestIT0140Phase1And2AcceptanceStillPassThroughPhase3ExtendedOrchestrator.testSensorFaultAndCrashAcceptanceUnaffectedByPhase3Extension</t>
         </is>
       </c>
     </row>
@@ -4225,7 +5964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4304,7 +6043,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.3 (Draft) — Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장, Phase 1/2 내용 유지</t>
         </is>
       </c>
     </row>
@@ -4423,6 +6162,38 @@
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장 — ENG-SWE2-001 v0.3 11장 15~21단계를 따라 IT-0094~IT-0140(47건) 신규 작성. IF-0021~IF-0023(신규 리프 3종) 및 확장된 IF-0001/IF-0005/IF-0007/IF-0008/IF-0020 전체를 대상으로 경계값(2.9/3.0/3.1km/h), 좌우 4조합(FF/FT/TF/TT), 우선순위 체인(4=ignition-off/5=ISOFIX/6=자동주행잠금) 상충, OFF 상태 전 조합, 오류 주입(vehicleSpeedField/isofix 필드/ignitionOnField invalid → OFF 미판정 회귀 포함)을 다룬다. test_it_step6/14의 Phase3 3개 협력객체(vehicleSpeedMonitor/isofixMonitor/ignitionOffReleaseMonitor) 배선을 재확인(coding 게이트의 기계적 동기화가 정확함을 확인, 정정 불필요).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
